--- a/DB/테이블명세서.xlsx
+++ b/DB/테이블명세서.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevPrograms\workspace\DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFACDC6-817F-4BBC-A502-AAC375D10E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC299A8-BC59-4AE7-BCFB-1875460BA1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
+    <workbookView minimized="1" xWindow="-4365" yWindow="3210" windowWidth="27765" windowHeight="7605" xr2:uid="{802E7722-B099-FB4F-89D0-B5B50B7F50C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Table Description" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="163">
   <si>
     <t>컬럼명</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -669,6 +669,10 @@
   </si>
   <si>
     <t xml:space="preserve">   배역명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장르</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1923,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
